--- a/isms-core-framework/A.8-technological-controls/isms-a.8.15-logging/WKBK/90_workbooks/ISMS-IMP-A.8.15.5_Compliance_Dashboard_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.15-logging/WKBK/90_workbooks/ISMS-IMP-A.8.15.5_Compliance_Dashboard_20260208.xlsx
@@ -6266,7 +6266,7 @@
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>PCI DSS 4.0</t>
+          <t>PCI DSS v4.0.1 4.0</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
@@ -8432,7 +8432,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A10:A159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ISO 27001,PCI DSS,HIPAA,GDPR,SOX,DORA,NIS2,FADP,Other"</formula1>
+      <formula1>"ISO 27001,PCI DSS v4.0.1,HIPAA,GDPR,SOX,DORA,NIS2,FADP,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="G10:G159" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✅ Compliant,⚠️ Partial,❌ Non-Compliant,➖ N/A"</formula1>
